--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios142.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios142.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34.39217015445931</v>
+        <v>29.60759092756935</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.6234297669879</v>
+        <v>31.68160568791494</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.766612268284</v>
+        <v>21.87499647279631</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.23741304757839</v>
+        <v>31.29283301540083</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34.78885266859874</v>
+        <v>33.55104533245376</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.73524966037872</v>
+        <v>25.8428605110534</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34.22629316841201</v>
+        <v>29.351527988344</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29.8301225771567</v>
+        <v>31.75301913241825</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23.91824989829777</v>
+        <v>22.13701833127479</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.30045213401321</v>
+        <v>31.11090321211513</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34.11004851082421</v>
+        <v>34.15053563983732</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.11206917168994</v>
+        <v>25.41824456984574</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29.289393147176</v>
+        <v>23.0456827824037</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.35806842957945</v>
+        <v>25.94413137489392</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28.58428493283596</v>
+        <v>31.09753005366366</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.55981691497177</v>
+        <v>28.47762803792343</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.28493104785662</v>
+        <v>26.73198290550498</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.0601575020961</v>
+        <v>23.86850635277376</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.23840724035502</v>
+        <v>22.96403137051147</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>26.46279716790448</v>
+        <v>26.34532502992343</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.20674666820404</v>
+        <v>31.16717840513755</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.96821568654851</v>
+        <v>28.07262859267497</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>33.03815274317244</v>
+        <v>27.17348138627122</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.46620390422534</v>
+        <v>24.29805396875646</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.98838669535289</v>
+        <v>31.5666360387097</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26.73552314454621</v>
+        <v>29.45960854523643</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31.34095608962843</v>
+        <v>25.23676669714619</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.10316724410544</v>
+        <v>27.48534474263754</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.76067091523272</v>
+        <v>28.78649423948327</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23.63389671771299</v>
+        <v>22.18428037571457</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.84324942106113</v>
+        <v>31.78583986222163</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>26.60623465333012</v>
+        <v>29.4953044052041</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31.29166716939785</v>
+        <v>24.52351643059636</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.62770980049567</v>
+        <v>27.20146577768916</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>36.02643026910879</v>
+        <v>28.67041867246017</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>23.15559754488435</v>
+        <v>22.38231847110046</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>34.02559788126603</v>
+        <v>33.7964157110325</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>28.88901299921978</v>
+        <v>27.1491233420536</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>23.58699549992685</v>
+        <v>30.96505280132508</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26.54636903236922</v>
+        <v>32.11919841425695</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>29.26305134047075</v>
+        <v>33.16423160720337</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26.86650417331837</v>
+        <v>24.2535676433354</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>34.42526933683789</v>
+        <v>33.93345477712734</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.0573897083627</v>
+        <v>27.26425190671874</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>23.37444306276344</v>
+        <v>30.45929965839861</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26.34678228137573</v>
+        <v>32.61001935462414</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.66299606447226</v>
+        <v>32.81809191646168</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>27.9752651002081</v>
+        <v>24.51317361572876</v>
       </c>
     </row>
   </sheetData>
